--- a/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -65,6 +65,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
   </si>
 </sst>
 </file>
@@ -614,7 +641,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -644,6 +671,75 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920023</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920049</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920022</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -67,31 +67,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
+    <t>ARIEL</t>
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
   </si>
   <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
+    <t>VICTOR ISRAEL</t>
   </si>
 </sst>
 </file>
@@ -557,16 +554,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.14</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -631,7 +631,7 @@
         <v>82.14</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -673,7 +673,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920023</v>
+        <v>21330051920012</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -682,7 +682,7 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -696,7 +696,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920049</v>
+        <v>21330051920023</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -705,7 +705,7 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -714,21 +714,21 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920022</v>
+        <v>21330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -70,9 +70,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
   </si>
   <si>
     <t>ARIEL</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
   </si>
   <si>
     <t>VICTOR ISRAEL</t>
@@ -622,16 +616,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -641,7 +635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -679,10 +673,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -696,16 +690,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920023</v>
+        <v>21330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -714,29 +708,6 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920015</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -67,22 +67,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
   </si>
 </sst>
 </file>
@@ -616,13 +619,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>82.14</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -635,7 +638,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -667,7 +670,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920012</v>
+        <v>20330051920366</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -690,13 +693,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920015</v>
+        <v>20330051920367</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -708,6 +711,29 @@
         <v>9</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920049</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>COYOHUA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>ELI ANTONIO</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
   </si>
   <si>
     <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
   </si>
 </sst>
 </file>
@@ -638,7 +644,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -679,7 +685,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -702,7 +708,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -725,7 +731,7 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -734,6 +740,29 @@
         <v>9</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920195</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
@@ -634,7 +634,7 @@
         <v>82.14</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20231.xlsx
@@ -634,7 +634,7 @@
         <v>82.14</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
